--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487178_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487178_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.3035</v>
+        <v>12.7844</v>
       </c>
       <c r="E2" t="n">
-        <v>10.7619</v>
+        <v>11.1625</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5416</v>
+        <v>1.6219</v>
       </c>
       <c r="G2" t="n">
         <v>6.035</v>
@@ -610,13 +610,13 @@
         <v>2.3161</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6736</v>
+        <v>-0.1927</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9518</v>
+        <v>-0.5512</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2783</v>
+        <v>0.3586</v>
       </c>
       <c r="V2" t="n">
         <v>4.626</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4138</v>
+        <v>4.5264</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6175</v>
+        <v>3.5159</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7963</v>
+        <v>1.0105</v>
       </c>
       <c r="G3" t="n">
         <v>3.3642</v>
@@ -688,13 +688,13 @@
         <v>2.1231</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0616</v>
+        <v>0.1742</v>
       </c>
       <c r="T3" t="n">
-        <v>1.289</v>
+        <v>0.1874</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2274</v>
+        <v>-0.0132</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9421</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8438</v>
+        <v>3.1581</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8322</v>
+        <v>2.9323</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0116</v>
+        <v>0.2258</v>
       </c>
       <c r="G4" t="n">
         <v>1.6036</v>
@@ -766,13 +766,13 @@
         <v>1.7371</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6597</v>
+        <v>-0.3454</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5354</v>
+        <v>-0.4352</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1243</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>1.5138</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6781</v>
+        <v>0.9544</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.1298</v>
+        <v>-1.7292</v>
       </c>
       <c r="F5" t="n">
-        <v>3.8079</v>
+        <v>2.6836</v>
       </c>
       <c r="G5" t="n">
         <v>0.1048</v>
@@ -844,13 +844,13 @@
         <v>1.7371</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6313</v>
+        <v>0.9075</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9518</v>
+        <v>-0.5512</v>
       </c>
       <c r="U5" t="n">
-        <v>2.5831</v>
+        <v>1.4588</v>
       </c>
       <c r="V5" t="n">
         <v>0.3281</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. BONILLA HERNANDEZ</t>
+          <t>M. KHATIASHVILI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0621</v>
+        <v>0.4068</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1953</v>
+        <v>-1.2497</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2575</v>
+        <v>1.6565</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4746</v>
+        <v>1.3547</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5496</v>
+        <v>2.0337</v>
       </c>
       <c r="I6" t="n">
-        <v>0.075</v>
+        <v>-0.679</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4333</v>
+        <v>2.4621</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3519</v>
+        <v>2.3078</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0814</v>
+        <v>0.1542</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9079</v>
+        <v>-1.1074</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9014</v>
+        <v>-0.2741</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0064</v>
+        <v>-0.8333</v>
       </c>
       <c r="P6" t="n">
-        <v>0.579</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-4.0532</v>
       </c>
       <c r="R6" t="n">
-        <v>0.579</v>
+        <v>2.3161</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1666</v>
+        <v>0.1752</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.238</v>
+        <v>-0.2726</v>
       </c>
       <c r="U6" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.4478</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. KHATIASHVILI</t>
+          <t>E. BONILLA HERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2278</v>
+        <v>0.2452</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7504</v>
+        <v>0.3956</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5227</v>
+        <v>-0.1504</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3547</v>
+        <v>-0.4746</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0337</v>
+        <v>-0.5496</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.679</v>
+        <v>0.075</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4621</v>
+        <v>0.4333</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3078</v>
+        <v>0.3519</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1542</v>
+        <v>0.0814</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1074</v>
+        <v>-0.9079</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2741</v>
+        <v>-0.9014</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8333</v>
+        <v>-0.0064</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.7371</v>
+        <v>0.579</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.0532</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3161</v>
+        <v>0.579</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4594</v>
+        <v>0.1408</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7733</v>
+        <v>-0.0377</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3139</v>
+        <v>0.1785</v>
       </c>
       <c r="V7" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5644</v>
+        <v>0.0503</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4094</v>
+        <v>0.8099</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9737</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7853</v>
@@ -1078,13 +1078,13 @@
         <v>2.5091</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8672</v>
+        <v>-0.2525</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7733</v>
+        <v>-0.3728</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0939</v>
+        <v>0.1203</v>
       </c>
       <c r="V8" t="n">
         <v>-1.228</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. IBARROLA ITURRIA</t>
+          <t>U. RUA ALVAREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7362</v>
+        <v>-0.3721</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3487</v>
+        <v>-0.6183</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0848</v>
+        <v>0.2461</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2848</v>
+        <v>0.3333</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4376</v>
+        <v>0.1833</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1528</v>
+        <v>0.1499</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6838</v>
+        <v>0.8197</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5693</v>
+        <v>0.1035</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2531</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9685</v>
+        <v>-0.4864</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8682</v>
+        <v>0.0798</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1003</v>
+        <v>-0.5662</v>
       </c>
       <c r="P9" t="n">
         <v>-0.579</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.158</v>
+        <v>-0.965</v>
       </c>
       <c r="R9" t="n">
-        <v>0.579</v>
+        <v>0.386</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5558999999999999</v>
+        <v>-0.7826</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2512</v>
+        <v>-0.4729</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3047</v>
+        <v>-0.3097</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5717</v>
+        <v>0.6562</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>U. RUA ALVAREZ</t>
+          <t>O. IBARROLA ITURRIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1276</v>
+        <v>-0.9166</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9187</v>
+        <v>0.2485</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2089</v>
+        <v>-1.1651</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3333</v>
+        <v>-1.2848</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1833</v>
+        <v>-1.4376</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1499</v>
+        <v>0.1528</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8197</v>
+        <v>0.6838</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1035</v>
+        <v>-0.5693</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7161999999999999</v>
+        <v>1.2531</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4864</v>
+        <v>-1.9685</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0798</v>
+        <v>-0.8682</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5662</v>
+        <v>-1.1003</v>
       </c>
       <c r="P10" t="n">
         <v>-0.579</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.965</v>
+        <v>-1.158</v>
       </c>
       <c r="R10" t="n">
-        <v>0.386</v>
+        <v>0.579</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5381</v>
+        <v>0.3754</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7733</v>
+        <v>0.151</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7648</v>
+        <v>0.2244</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6562</v>
+        <v>0.5717</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7725</v>
+        <v>-3.115</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6186</v>
+        <v>-2.7202</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1538</v>
+        <v>-0.3948</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7642</v>
@@ -1312,13 +1312,13 @@
         <v>2.1231</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6359</v>
+        <v>0.2935</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1105</v>
+        <v>0.0089</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5255</v>
+        <v>0.2845</v>
       </c>
       <c r="V11" t="n">
         <v>1.5138</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2004</v>
+        <v>-3.1736</v>
       </c>
       <c r="E12" t="n">
         <v>-1.2363</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9641</v>
+        <v>-1.9373</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4462</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3682</v>
+        <v>-0.3414</v>
       </c>
       <c r="T12" t="n">
         <v>-0.119</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2492</v>
+        <v>-0.2224</v>
       </c>
       <c r="V12" t="n">
         <v>-1.228</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.5482</v>
+        <v>14.5483</v>
       </c>
       <c r="E13" t="n">
-        <v>11.5112</v>
+        <v>11.511</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0373</v>
+        <v>3.0372</v>
       </c>
       <c r="G13" t="n">
         <v>6.040499999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>4.672999999999999</v>
+        <v>4.673000000000001</v>
       </c>
       <c r="I13" t="n">
         <v>1.367400000000001</v>
@@ -1468,13 +1468,13 @@
         <v>16.4057</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1519</v>
+        <v>0.1520000000000002</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.465199999999999</v>
+        <v>-2.4653</v>
       </c>
       <c r="U13" t="n">
-        <v>2.6173</v>
+        <v>2.6175</v>
       </c>
       <c r="V13" t="n">
         <v>6.4255</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6931</v>
+        <v>5.1264</v>
       </c>
       <c r="E14" t="n">
-        <v>5.0677</v>
+        <v>5.7687</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3746</v>
+        <v>-0.6423</v>
       </c>
       <c r="G14" t="n">
         <v>3.1927</v>
@@ -1546,13 +1546,13 @@
         <v>2.3161</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6227</v>
+        <v>-0.1894</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4277</v>
+        <v>-0.7267</v>
       </c>
       <c r="U14" t="n">
-        <v>0.805</v>
+        <v>0.5373</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. ERRASTI URANGA</t>
+          <t>U. CONDE LAKUNTZA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5654</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8441</v>
+        <v>2.5168</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2787</v>
+        <v>-1.5768</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5733</v>
+        <v>1.1558</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0621</v>
+        <v>0.0248</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5112</v>
+        <v>1.131</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7477</v>
+        <v>3.1244</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1758</v>
+        <v>1.2936</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5719</v>
+        <v>1.8308</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1744</v>
+        <v>-1.9685</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1137</v>
+        <v>-1.2688</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.0607</v>
+        <v>-0.6998</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.386</v>
+        <v>-0.579</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1231</v>
+        <v>-1.9301</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7371</v>
+        <v>1.3511</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7641</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9915</v>
+        <v>-0.1913</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2274</v>
+        <v>0.2687</v>
       </c>
       <c r="V15" t="n">
-        <v>0.614</v>
+        <v>0.2859</v>
       </c>
       <c r="W15" t="n">
-        <v>1.228</v>
+        <v>1.5138</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.614</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. CONDE LAKUNTZA</t>
+          <t>E. ERRASTI URANGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0203</v>
+        <v>0.7782</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4175</v>
+        <v>1.8427</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4379</v>
+        <v>-1.0646</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1859</v>
+        <v>0.5733</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0877</v>
+        <v>0.0621</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9018</v>
+        <v>0.5112</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6555</v>
+        <v>2.7477</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0207</v>
+        <v>0.1758</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6348</v>
+        <v>2.5719</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8414</v>
+        <v>-2.1744</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1084</v>
+        <v>-0.1137</v>
       </c>
       <c r="O16" t="n">
-        <v>0.267</v>
+        <v>-2.0607</v>
       </c>
       <c r="P16" t="n">
-        <v>0.579</v>
+        <v>-0.386</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.1231</v>
       </c>
       <c r="R16" t="n">
-        <v>0.579</v>
+        <v>1.7371</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1276</v>
+        <v>-0.0231</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.238</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1104</v>
+        <v>-0.0132</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2859</v>
+        <v>0.614</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2859</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>U. CONDE LAKUNTZA</t>
+          <t>E. CONDE LAKUNTZA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1625</v>
+        <v>-0.0005</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8158</v>
+        <v>0.5177</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9783</v>
+        <v>-0.5182</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1558</v>
+        <v>-0.1859</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0248</v>
+        <v>-1.0877</v>
       </c>
       <c r="I17" t="n">
-        <v>1.131</v>
+        <v>0.9018</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1244</v>
+        <v>0.6555</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2936</v>
+        <v>0.0207</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8308</v>
+        <v>0.6348</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9685</v>
+        <v>-0.8414</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2688</v>
+        <v>-1.1084</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6998</v>
+        <v>0.267</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.579</v>
+        <v>0.579</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0252</v>
+        <v>-0.1077</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8923</v>
+        <v>-0.1378</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1329</v>
+        <v>0.0301</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2859</v>
+        <v>-0.2859</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.228</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2013</v>
+        <v>-0.8672</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4078</v>
+        <v>-1.2075</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2065</v>
+        <v>0.3403</v>
       </c>
       <c r="G18" t="n">
         <v>-1.8841</v>
@@ -1858,13 +1858,13 @@
         <v>1.158</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4752</v>
+        <v>-0.1411</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2974</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1778</v>
+        <v>-0.044</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2516</v>
+        <v>-2.1852</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2815</v>
+        <v>-2.0812</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0299</v>
+        <v>-0.104</v>
       </c>
       <c r="G19" t="n">
         <v>-2.0143</v>
@@ -1936,13 +1936,13 @@
         <v>0.965</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2373</v>
+        <v>-0.1709</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4759</v>
+        <v>-0.2756</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2386</v>
+        <v>0.1048</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4592</v>
+        <v>-2.8597</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.776</v>
+        <v>-2.1765</v>
       </c>
       <c r="F20" t="n">
         <v>-0.6832</v>
@@ -2014,10 +2014,10 @@
         <v>1.7371</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6821</v>
+        <v>0.2816</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3239</v>
+        <v>-0.0766</v>
       </c>
       <c r="U20" t="n">
         <v>0.3582</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3344</v>
+        <v>-3.6953</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2876</v>
+        <v>-1.4878</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0468</v>
+        <v>-2.2074</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6957</v>
@@ -2092,13 +2092,13 @@
         <v>1.158</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3384</v>
+        <v>-0.0225</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0462</v>
+        <v>-0.2465</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3847</v>
+        <v>0.2241</v>
       </c>
       <c r="V21" t="n">
         <v>-2.1701</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5953</v>
+        <v>-4.7177</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9791</v>
+        <v>-2.7802</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6162</v>
+        <v>-1.9375</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2836</v>
@@ -2170,13 +2170,13 @@
         <v>1.7371</v>
       </c>
       <c r="S22" t="n">
-        <v>1.5375</v>
+        <v>0.4151</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6346000000000001</v>
+        <v>-0.1665</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9029</v>
+        <v>0.5816</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4982</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.7823</v>
+        <v>-7.0674</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4506</v>
+        <v>-3.9499</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.3317</v>
+        <v>-3.1175</v>
       </c>
       <c r="G23" t="n">
         <v>-0.094</v>
@@ -2248,13 +2248,13 @@
         <v>1.7371</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9862</v>
+        <v>-0.2713</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1898</v>
+        <v>-0.6891</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2036</v>
+        <v>0.4177</v>
       </c>
       <c r="V23" t="n">
         <v>-2.4559</v>
@@ -2284,10 +2284,10 @@
         <v>-14.5484</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.037500000000001</v>
+        <v>-3.0372</v>
       </c>
       <c r="F24" t="n">
-        <v>-11.511</v>
+        <v>-11.5112</v>
       </c>
       <c r="G24" t="n">
         <v>-6.040600000000001</v>
@@ -2296,7 +2296,7 @@
         <v>-4.6732</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.367400000000001</v>
+        <v>-1.3674</v>
       </c>
       <c r="J24" t="n">
         <v>13.9425</v>
@@ -2326,10 +2326,10 @@
         <v>14.4756</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1520999999999998</v>
+        <v>-0.152</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.6173</v>
+        <v>-2.6172</v>
       </c>
       <c r="U24" t="n">
         <v>2.4653</v>
